--- a/data/trans_orig/Predimed-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Predimed-Habitat-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media de la escala de adherencia a la dieta mediterránea (Predimed)</t>
+          <t>Puntuación media de la escala de adherencia a la dieta mediterránea (Predimed) (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 7,08</t>
+          <t>6,71; 7,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,0</t>
+          <t>6,71; 7,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,76; 6,98</t>
+          <t>6,75; 6,98</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 6,71</t>
+          <t>6,11; 6,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 6,54</t>
+          <t>6,16; 6,55</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 6,47</t>
+          <t>6,05; 6,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 7,46</t>
+          <t>6,38; 7,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 7,23</t>
+          <t>6,3; 7,11</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 6,58</t>
+          <t>6,32; 6,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 6,52</t>
+          <t>6,3; 6,52</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 6,85</t>
+          <t>6,44; 6,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,42; 6,67</t>
+          <t>6,42; 6,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Predimed-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Predimed-Habitat-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>6,87</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,85</t>
+          <t>6,8</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>6,83</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 7,07</t>
+          <t>6,68; 7,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 7,0</t>
+          <t>6,64; 6,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 6,98</t>
+          <t>6,72; 6,96</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>6,2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,24</t>
+          <t>6,21</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,31</t>
+          <t>6,21</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 6,69</t>
+          <t>6,02; 6,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 6,38</t>
+          <t>6,07; 6,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 6,55</t>
+          <t>6,11; 6,32</t>
         </is>
       </c>
     </row>
@@ -653,12 +653,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>6,38</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,61</t>
+          <t>6,32</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 6,48</t>
+          <t>6,03; 6,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 7,45</t>
+          <t>6,24; 6,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 7,11</t>
+          <t>6,19; 6,44</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,37</t>
+          <t>6,3</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,46</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,42</t>
+          <t>6,36</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 6,53</t>
+          <t>6,13; 6,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 6,59</t>
+          <t>6,28; 6,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 6,52</t>
+          <t>6,25; 6,45</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,44</t>
+          <t>6,37</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>6,42</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>6,4</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 6,57</t>
+          <t>6,28; 6,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 6,88</t>
+          <t>6,35; 6,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,42; 6,68</t>
+          <t>6,33; 6,45</t>
         </is>
       </c>
     </row>
